--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>104033</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468479.432345806</v>
+        <v>468479</v>
       </c>
       <c r="R2" t="n">
-        <v>6428348.229395022</v>
+        <v>6428348</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106447</v>
+        <v>106456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106456</v>
+        <v>106461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106461</v>
+        <v>106489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106489</v>
+        <v>106495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106495</v>
+        <v>106502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106502</v>
+        <v>106506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106506</v>
+        <v>106513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106516</v>
+        <v>106521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106521</v>
+        <v>106529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106529</v>
+        <v>106539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34359-2025 artfynd.xlsx
+++ b/artfynd/A 34359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75133090</v>
       </c>
       <c r="B2" t="n">
-        <v>106539</v>
+        <v>107060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
